--- a/data/pds_node_classification.xlsx
+++ b/data/pds_node_classification.xlsx
@@ -595,13 +595,13 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>JPL</t>
+          <t>IMG</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>JPL</t>
+          <t>IMG</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -636,13 +636,13 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>JPL</t>
+          <t>IMG</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>JPL</t>
+          <t>IMG</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>JPL</t>
+          <t>IMG</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>RMS,JPL</t>
+          <t>RMS,IMG</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1022,13 +1022,13 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>JPL</t>
+          <t>IMG</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>JPL</t>
+          <t>IMG</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1139,7 +1139,11 @@
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr"/>
-      <c r="E17" s="2" t="inlineStr"/>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>GEO</t>
+        </is>
+      </c>
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr"/>
@@ -1424,7 +1428,11 @@
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr"/>
-      <c r="E24" s="2" t="inlineStr"/>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>GEO</t>
+        </is>
+      </c>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr"/>
@@ -1508,7 +1516,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>JPL</t>
+          <t>RMS</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1518,7 +1526,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>JPL,RMS</t>
+          <t>IMG,RMS</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1680,13 +1688,13 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>JPL</t>
+          <t>IMG</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>JPL</t>
+          <t>IMG</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -1722,13 +1730,13 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>JPL</t>
+          <t>RMS</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>JPL</t>
+          <t>IMG</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -1769,12 +1777,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>JPL</t>
+          <t>IMG</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>GEO,JPL</t>
+          <t>GEO,IMG</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -1938,13 +1946,13 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>JPL</t>
+          <t>IMG</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>JPL</t>
+          <t>IMG</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2599,13 +2607,13 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>JPL</t>
+          <t>IMG</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>JPL</t>
+          <t>IMG</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -2765,13 +2773,13 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>JPL</t>
+          <t>IMG</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>JPL</t>
+          <t>IMG</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -2845,13 +2853,13 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>JPL</t>
+          <t>RMS</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>JPL</t>
+          <t>IMG</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3021,12 +3029,12 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>JPL</t>
+          <t>IMG</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>RMS,JPL</t>
+          <t>RMS,IMG</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3064,13 +3072,13 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>JPL</t>
+          <t>RMS</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr"/>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>JPL</t>
+          <t>IMG</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3106,7 +3114,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>JPL</t>
+          <t>IMG</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -3116,7 +3124,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>JPL,GEO</t>
+          <t>IMG,GEO</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3155,13 +3163,13 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>JPL</t>
+          <t>IMG</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr"/>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>JPL</t>
+          <t>IMG</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3646,7 +3654,11 @@
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr"/>
-      <c r="E77" s="2" t="inlineStr"/>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>GEO</t>
+        </is>
+      </c>
       <c r="F77" s="2" t="inlineStr"/>
       <c r="G77" s="2" t="inlineStr"/>
       <c r="H77" s="2" t="inlineStr"/>
@@ -3817,12 +3829,12 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>JPL</t>
+          <t>IMG</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>GEO,JPL</t>
+          <t>GEO,IMG</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -3868,12 +3880,12 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>JPL</t>
+          <t>IMG</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>RMS,JPL</t>
+          <t>RMS,IMG</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -4117,13 +4129,13 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>JPL</t>
+          <t>RMS</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr"/>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>JPL</t>
+          <t>IMG</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -4499,12 +4511,12 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>JPL</t>
+          <t>IMG</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>GEO,JPL</t>
+          <t>GEO,IMG</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -4588,32 +4600,32 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Geosciences Node — surface geology/geophysics (HRSC, CRISM, MOLA, Magellan, M3, LOLA, DLRE, APXS, MTES)</t>
+          <t>Geosciences Node — surface geology/geophysics (CRISM, HRSC DTM, Magellan GxDR, MOLA, M3, LOLA, DLRE, MER MTES/APXS)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>JPL</t>
+          <t>IMG</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Imaging Node @ JPL — non-lunar imaging (HiRISE, CTX, MDIS, MER cameras, Cassini ISS/VIMS)</t>
+          <t>Imaging Node @ JPL — non-lunar imaging (HiRISE, CTX, MESSENGER MDIS, MER Pancam/Navcam/MI, Cassini ISS — when archive at IMG)</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4679,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Planetary Plasma Interactions — fields &amp; particles (Juno FGM/JED/JAD/WAV, Cassini MAG, MESSENGER MAG/EPPS-FIPS)</t>
+          <t>Planetary Plasma Interactions — fields &amp; particles (Juno FGM/JAD/JED/WAV, Cassini MAG, MESSENGER MAG/EPPS-FIPS)</t>
         </is>
       </c>
     </row>
@@ -4678,14 +4690,14 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ring-Moon Systems Node — Cassini UVIS, ring observations</t>
+          <t>Ring-Moon Systems Node — Cassini ISS/UVIS/VIMS for rings + Saturn satellites (incl. Titan VIMS, Enceladus plume, Rhea UVIS)</t>
         </is>
       </c>
     </row>
@@ -4703,7 +4715,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Small Bodies Node — asteroids/comets (Dawn, NEAR, OSIRIS-REx)</t>
+          <t>Small Bodies Node — asteroids/comets (Dawn at Ceres, NEAR at Eros, OSIRIS-REx at Bennu)</t>
         </is>
       </c>
     </row>
